--- a/employee_surveys/026_excellence_and_dedication_survey--employee_surveys.xlsx
+++ b/employee_surveys/026_excellence_and_dedication_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employee_engagement',_'label':_'employee_engagement'}</t>
+          <t>employee_engagement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Employee engagement', 'label': 'Employee engagement'}</t>
+          <t>Employee engagement</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'company_culture',_'label':_'company_culture'}</t>
+          <t>company_culture</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Company culture', 'label': 'Company culture'}</t>
+          <t>Company culture</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'job_fit',_'label':_'job_fit'}</t>
+          <t>job_fit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Job fit', 'label': 'Job fit'}</t>
+          <t>Job fit</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'benefits',_'label':_'benefits'}</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Benefits', 'label': 'Benefits'}</t>
+          <t>Benefits</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'professional_development',_'label':_'professional_development'}</t>
+          <t>professional_development</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Professional development', 'label': 'Professional development'}</t>
+          <t>Professional development</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'work_life_balance',_'label':_'work_life_balance'}</t>
+          <t>work_life_balance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Work life balance', 'label': 'Work life balance'}</t>
+          <t>Work life balance</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'management',_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Management', 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_feel_valued',_'label':_'i_feel_valued'}</t>
+          <t>i_feel_valued</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I feel valued', 'label': 'I feel valued'}</t>
+          <t>I feel valued</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'i_feel_respected',_'label':_'i_feel_respected'}</t>
+          <t>i_feel_respected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'I feel respected', 'label': 'I feel respected'}</t>
+          <t>I feel respected</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'i_feel_supported',_'label':_'i_feel_supported'}</t>
+          <t>i_feel_supported</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'I feel supported', 'label': 'I feel supported'}</t>
+          <t>I feel supported</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'i_feel_engaged',_'label':_'i_feel_engaged'}</t>
+          <t>i_feel_engaged</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'I feel engaged', 'label': 'I feel engaged'}</t>
+          <t>I feel engaged</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'i_feel_happy',_'label':_'i_feel_happy'}</t>
+          <t>i_feel_happy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'I feel happy', 'label': 'I feel happy'}</t>
+          <t>I feel happy</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'address',_'label':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Address', 'label': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'something_we_do_not_have',_'label':_'something_we_do_not_have'}</t>
+          <t>something_we_do_not_have</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Something we do not have', 'label': 'Something we do not have'}</t>
+          <t>Something we do not have</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'something_we_are_doing_poorly',_'label':_'something_we_are_doing_poorly'}</t>
+          <t>something_we_are_doing_poorly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Something we are doing poorly', 'label': 'Something we are doing poorly'}</t>
+          <t>Something we are doing poorly</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'something_we_are_doing_well',_'label':_'something_we_are_doing_well'}</t>
+          <t>something_we_are_doing_well</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Something we are doing well', 'label': 'Something we are doing well'}</t>
+          <t>Something we are doing well</t>
         </is>
       </c>
     </row>
